--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_OV.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>795.3625414706461</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>475.4013437469266</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>390.6279785442159</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>370.4798607314091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2602.825699863442</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1617.062296026407</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1151.048916303433</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>945.8714456117898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>389.6230887972488</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>262.5000129926961</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>253.9793968266578</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>255.7124706025494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>57.9931633492053</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>36.93277136971746</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>36.98338595019789</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>41.3356935164956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>151.1694474754234</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>104.0276315578219</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>112.7777915265681</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>121.143424118054</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
